--- a/Excel/Avg/Rata-rata-64.xlsx
+++ b/Excel/Avg/Rata-rata-64.xlsx
@@ -620,22 +620,22 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>0.0300845</v>
+        <v>0.0332437</v>
       </c>
       <c r="C2">
-        <v>0.019613</v>
+        <v>0.0225962</v>
       </c>
       <c r="D2">
-        <v>0.0169623</v>
+        <v>0.0197346</v>
       </c>
       <c r="E2">
-        <v>0.02975870000000001</v>
+        <v>0.034541</v>
       </c>
       <c r="F2">
-        <v>0.0501643</v>
+        <v>0.0576618</v>
       </c>
       <c r="G2">
-        <v>0.02931656</v>
+        <v>0.03355546</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -643,22 +643,22 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.006245000000000001</v>
+        <v>0.0072085</v>
       </c>
       <c r="C3">
-        <v>0.0051652</v>
+        <v>0.005907599999999999</v>
       </c>
       <c r="D3">
-        <v>0.004333999999999999</v>
+        <v>0.0050262</v>
       </c>
       <c r="E3">
-        <v>0.0051504</v>
+        <v>0.005967200000000001</v>
       </c>
       <c r="F3">
-        <v>0.003795000000000001</v>
+        <v>0.004460500000000001</v>
       </c>
       <c r="G3">
-        <v>0.00493792</v>
+        <v>0.005713999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -666,22 +666,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>0.0260971</v>
+        <v>0.02965060000000001</v>
       </c>
       <c r="C4">
-        <v>0.0172503</v>
+        <v>0.0194719</v>
       </c>
       <c r="D4">
-        <v>0.008766900000000001</v>
+        <v>0.0100701</v>
       </c>
       <c r="E4">
-        <v>0.004695099999999999</v>
+        <v>0.005492700000000001</v>
       </c>
       <c r="F4">
-        <v>0.0048049</v>
+        <v>0.0054637</v>
       </c>
       <c r="G4">
-        <v>0.01232286</v>
+        <v>0.0140298</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -689,22 +689,22 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0.0263918</v>
+        <v>0.0304034</v>
       </c>
       <c r="C5">
-        <v>0.0165019</v>
+        <v>0.0188644</v>
       </c>
       <c r="D5">
-        <v>0.0136829</v>
+        <v>0.0156049</v>
       </c>
       <c r="E5">
-        <v>0.018626</v>
+        <v>0.0211114</v>
       </c>
       <c r="F5">
-        <v>0.0239725</v>
+        <v>0.0280113</v>
       </c>
       <c r="G5">
-        <v>0.01983502</v>
+        <v>0.02279908</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -712,22 +712,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.007489</v>
+        <v>0.008776600000000001</v>
       </c>
       <c r="C6">
-        <v>0.0035506</v>
+        <v>0.0040957</v>
       </c>
       <c r="D6">
-        <v>0.0050197</v>
+        <v>0.005856600000000001</v>
       </c>
       <c r="E6">
-        <v>0.0050564</v>
+        <v>0.0059741</v>
       </c>
       <c r="F6">
-        <v>0.008039800000000001</v>
+        <v>0.0093258</v>
       </c>
       <c r="G6">
-        <v>0.005831100000000001</v>
+        <v>0.006805759999999999</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -735,22 +735,22 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>0.02909</v>
+        <v>0.033621</v>
       </c>
       <c r="C7">
-        <v>0.0197748</v>
+        <v>0.02283139999999999</v>
       </c>
       <c r="D7">
-        <v>0.0170541</v>
+        <v>0.0196953</v>
       </c>
       <c r="E7">
-        <v>0.0296858</v>
+        <v>0.03443719999999999</v>
       </c>
       <c r="F7">
-        <v>0.0501517</v>
+        <v>0.0578503</v>
       </c>
       <c r="G7">
-        <v>0.02915128</v>
+        <v>0.03368703999999999</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -758,22 +758,22 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>0.0292461</v>
+        <v>0.0335618</v>
       </c>
       <c r="C8">
-        <v>0.0187141</v>
+        <v>0.0211572</v>
       </c>
       <c r="D8">
-        <v>0.0148261</v>
+        <v>0.0171031</v>
       </c>
       <c r="E8">
-        <v>0.028206</v>
+        <v>0.0322826</v>
       </c>
       <c r="F8">
-        <v>0.0519604</v>
+        <v>0.0576528</v>
       </c>
       <c r="G8">
-        <v>0.02859054</v>
+        <v>0.0323515</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -781,22 +781,22 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>0.0102976</v>
+        <v>0.011875</v>
       </c>
       <c r="C9">
-        <v>0.008888400000000001</v>
+        <v>0.0102671</v>
       </c>
       <c r="D9">
-        <v>0.0046809</v>
+        <v>0.005509600000000001</v>
       </c>
       <c r="E9">
-        <v>0.0033801</v>
+        <v>0.0039529</v>
       </c>
       <c r="F9">
-        <v>0.0025002</v>
+        <v>0.0029194</v>
       </c>
       <c r="G9">
-        <v>0.005949440000000001</v>
+        <v>0.0069048</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -804,22 +804,22 @@
         <v>15</v>
       </c>
       <c r="B10">
-        <v>0.0069059</v>
+        <v>0.007937500000000002</v>
       </c>
       <c r="C10">
-        <v>0.0061828</v>
+        <v>0.0070461</v>
       </c>
       <c r="D10">
-        <v>0.0040442</v>
+        <v>0.0045363</v>
       </c>
       <c r="E10">
-        <v>0.006343300000000001</v>
+        <v>0.007394300000000001</v>
       </c>
       <c r="F10">
-        <v>0.005200600000000001</v>
+        <v>0.0060795</v>
       </c>
       <c r="G10">
-        <v>0.00573536</v>
+        <v>0.006598740000000001</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -827,22 +827,22 @@
         <v>16</v>
       </c>
       <c r="B11">
-        <v>0.0065929</v>
+        <v>0.0075407</v>
       </c>
       <c r="C11">
-        <v>0.0056706</v>
+        <v>0.006258700000000001</v>
       </c>
       <c r="D11">
-        <v>0.004535200000000001</v>
+        <v>0.0052008</v>
       </c>
       <c r="E11">
-        <v>0.0053764</v>
+        <v>0.006779400000000001</v>
       </c>
       <c r="F11">
-        <v>0.004092699999999999</v>
+        <v>0.004715799999999999</v>
       </c>
       <c r="G11">
-        <v>0.005253559999999999</v>
+        <v>0.006099080000000001</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -850,22 +850,22 @@
         <v>17</v>
       </c>
       <c r="B12">
-        <v>0.006696199999999999</v>
+        <v>0.007845099999999999</v>
       </c>
       <c r="C12">
-        <v>0.005672399999999999</v>
+        <v>0.006692099999999999</v>
       </c>
       <c r="D12">
-        <v>0.0043631</v>
+        <v>0.0056385</v>
       </c>
       <c r="E12">
-        <v>0.005228500000000001</v>
+        <v>0.0068653</v>
       </c>
       <c r="F12">
-        <v>0.004308500000000001</v>
+        <v>0.0050372</v>
       </c>
       <c r="G12">
-        <v>0.00525374</v>
+        <v>0.00641564</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -873,22 +873,22 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>0.0262355</v>
+        <v>0.0299779</v>
       </c>
       <c r="C13">
-        <v>0.0174965</v>
+        <v>0.0198619</v>
       </c>
       <c r="D13">
-        <v>0.0089468</v>
+        <v>0.0102079</v>
       </c>
       <c r="E13">
-        <v>0.004957</v>
+        <v>0.005836599999999999</v>
       </c>
       <c r="F13">
-        <v>0.0050933</v>
+        <v>0.005794100000000001</v>
       </c>
       <c r="G13">
-        <v>0.01254582</v>
+        <v>0.01433568</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -896,22 +896,22 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>0.030114</v>
+        <v>0.0344098</v>
       </c>
       <c r="C14">
-        <v>0.0172479</v>
+        <v>0.0196019</v>
       </c>
       <c r="D14">
-        <v>0.0101272</v>
+        <v>0.0116858</v>
       </c>
       <c r="E14">
-        <v>0.0049015</v>
+        <v>0.005697499999999999</v>
       </c>
       <c r="F14">
-        <v>0.0048674</v>
+        <v>0.0055683</v>
       </c>
       <c r="G14">
-        <v>0.0134516</v>
+        <v>0.01539266</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -919,22 +919,22 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>0.03332020000000001</v>
+        <v>0.0385138</v>
       </c>
       <c r="C15">
-        <v>0.0217295</v>
+        <v>0.0249511</v>
       </c>
       <c r="D15">
-        <v>0.0105198</v>
+        <v>0.012089</v>
       </c>
       <c r="E15">
-        <v>0.0056214</v>
+        <v>0.006537200000000002</v>
       </c>
       <c r="F15">
-        <v>0.0116133</v>
+        <v>0.0145629</v>
       </c>
       <c r="G15">
-        <v>0.01656084</v>
+        <v>0.0193308</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -942,22 +942,22 @@
         <v>21</v>
       </c>
       <c r="B16">
-        <v>0.0265063</v>
+        <v>0.0309026</v>
       </c>
       <c r="C16">
-        <v>0.0168301</v>
+        <v>0.019244</v>
       </c>
       <c r="D16">
-        <v>0.0138365</v>
+        <v>0.0159433</v>
       </c>
       <c r="E16">
-        <v>0.0186439</v>
+        <v>0.0213723</v>
       </c>
       <c r="F16">
-        <v>0.0242281</v>
+        <v>0.028146</v>
       </c>
       <c r="G16">
-        <v>0.02000898</v>
+        <v>0.02312164</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -965,22 +965,22 @@
         <v>22</v>
       </c>
       <c r="B17">
-        <v>0.0256845</v>
+        <v>0.0298587</v>
       </c>
       <c r="C17">
-        <v>0.016619</v>
+        <v>0.019203</v>
       </c>
       <c r="D17">
-        <v>0.0135952</v>
+        <v>0.0157999</v>
       </c>
       <c r="E17">
-        <v>0.0178973</v>
+        <v>0.0207588</v>
       </c>
       <c r="F17">
-        <v>0.0202813</v>
+        <v>0.0234543</v>
       </c>
       <c r="G17">
-        <v>0.01881546</v>
+        <v>0.02181494</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -988,22 +988,22 @@
         <v>23</v>
       </c>
       <c r="B18">
-        <v>0.0046153</v>
+        <v>0.0053299</v>
       </c>
       <c r="C18">
-        <v>0.003033</v>
+        <v>0.0034984</v>
       </c>
       <c r="D18">
-        <v>0.0041219</v>
+        <v>0.0047555</v>
       </c>
       <c r="E18">
-        <v>0.003013</v>
+        <v>0.0035926</v>
       </c>
       <c r="F18">
-        <v>0.0060882</v>
+        <v>0.0070136</v>
       </c>
       <c r="G18">
-        <v>0.004174280000000001</v>
+        <v>0.004838</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1011,22 +1011,22 @@
         <v>24</v>
       </c>
       <c r="B19">
-        <v>0.004426100000000001</v>
+        <v>0.0050793</v>
       </c>
       <c r="C19">
-        <v>0.003272</v>
+        <v>0.0038275</v>
       </c>
       <c r="D19">
-        <v>0.0019604</v>
+        <v>0.0022023</v>
       </c>
       <c r="E19">
-        <v>0.0024747</v>
+        <v>0.0029741</v>
       </c>
       <c r="F19">
-        <v>0.0037186</v>
+        <v>0.004312499999999999</v>
       </c>
       <c r="G19">
-        <v>0.00317036</v>
+        <v>0.00367914</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1034,22 +1034,22 @@
         <v>25</v>
       </c>
       <c r="B20">
-        <v>0.0062226</v>
+        <v>0.0071132</v>
       </c>
       <c r="C20">
-        <v>0.0037772</v>
+        <v>0.004378000000000001</v>
       </c>
       <c r="D20">
-        <v>0.0040626</v>
+        <v>0.0045764</v>
       </c>
       <c r="E20">
-        <v>0.0038961</v>
+        <v>0.0046044</v>
       </c>
       <c r="F20">
-        <v>0.0065545</v>
+        <v>0.007651500000000001</v>
       </c>
       <c r="G20">
-        <v>0.0049026</v>
+        <v>0.005664700000000001</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1057,22 +1057,22 @@
         <v>26</v>
       </c>
       <c r="B21">
-        <v>0.007500999999999999</v>
+        <v>0.008748199999999999</v>
       </c>
       <c r="C21">
-        <v>0.003600299999999999</v>
+        <v>0.004168400000000001</v>
       </c>
       <c r="D21">
-        <v>0.0050514</v>
+        <v>0.005883</v>
       </c>
       <c r="E21">
-        <v>0.005144</v>
+        <v>0.0060451</v>
       </c>
       <c r="F21">
-        <v>0.008114100000000001</v>
+        <v>0.0094141</v>
       </c>
       <c r="G21">
-        <v>0.00588216</v>
+        <v>0.00685176</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1080,22 +1080,22 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>0.008067300000000001</v>
+        <v>0.0086467</v>
       </c>
       <c r="C22">
-        <v>0.0031847</v>
+        <v>0.0041194</v>
       </c>
       <c r="D22">
-        <v>0.004760499999999999</v>
+        <v>0.006092700000000001</v>
       </c>
       <c r="E22">
-        <v>0.0049699</v>
+        <v>0.0057946</v>
       </c>
       <c r="F22">
-        <v>0.007746099999999999</v>
+        <v>0.009351999999999999</v>
       </c>
       <c r="G22">
-        <v>0.005745699999999999</v>
+        <v>0.006801080000000001</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1103,22 +1103,22 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>0.0293555</v>
+        <v>0.0336776</v>
       </c>
       <c r="C23">
-        <v>0.0188002</v>
+        <v>0.0214685</v>
       </c>
       <c r="D23">
-        <v>0.0153584</v>
+        <v>0.0173737</v>
       </c>
       <c r="E23">
-        <v>0.0282388</v>
+        <v>0.032459</v>
       </c>
       <c r="F23">
-        <v>0.05150780000000001</v>
+        <v>0.05818589999999999</v>
       </c>
       <c r="G23">
-        <v>0.02865214</v>
+        <v>0.03263294</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1126,22 +1126,22 @@
         <v>29</v>
       </c>
       <c r="B24">
-        <v>0.0107272</v>
+        <v>0.0125902</v>
       </c>
       <c r="C24">
-        <v>0.009185599999999999</v>
+        <v>0.0106152</v>
       </c>
       <c r="D24">
-        <v>0.004921699999999999</v>
+        <v>0.005611199999999999</v>
       </c>
       <c r="E24">
-        <v>0.0036339</v>
+        <v>0.0041292</v>
       </c>
       <c r="F24">
-        <v>0.0028127</v>
+        <v>0.0031756</v>
       </c>
       <c r="G24">
-        <v>0.006256219999999998</v>
+        <v>0.007224280000000001</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1149,22 +1149,22 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>0.0113215</v>
+        <v>0.0133764</v>
       </c>
       <c r="C25">
-        <v>0.009476799999999999</v>
+        <v>0.0112279</v>
       </c>
       <c r="D25">
-        <v>0.005647399999999999</v>
+        <v>0.006625300000000001</v>
       </c>
       <c r="E25">
-        <v>0.0034827</v>
+        <v>0.004203399999999999</v>
       </c>
       <c r="F25">
-        <v>0.0025151</v>
+        <v>0.0030271</v>
       </c>
       <c r="G25">
-        <v>0.006488699999999998</v>
+        <v>0.007692019999999999</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1172,22 +1172,22 @@
         <v>31</v>
       </c>
       <c r="B26">
-        <v>0.011309</v>
+        <v>0.0131747</v>
       </c>
       <c r="C26">
-        <v>0.0142595</v>
+        <v>0.0165521</v>
       </c>
       <c r="D26">
-        <v>0.006864600000000001</v>
+        <v>0.008055900000000001</v>
       </c>
       <c r="E26">
-        <v>0.004038000000000001</v>
+        <v>0.004792</v>
       </c>
       <c r="F26">
-        <v>0.008003199999999999</v>
+        <v>0.0092871</v>
       </c>
       <c r="G26">
-        <v>0.008894859999999999</v>
+        <v>0.01037236</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1195,22 +1195,22 @@
         <v>32</v>
       </c>
       <c r="B27">
-        <v>0.0072632</v>
+        <v>0.008307999999999999</v>
       </c>
       <c r="C27">
-        <v>0.0064419</v>
+        <v>0.007364100000000001</v>
       </c>
       <c r="D27">
-        <v>0.0042303</v>
+        <v>0.004942199999999999</v>
       </c>
       <c r="E27">
-        <v>0.006577899999999999</v>
+        <v>0.007728500000000001</v>
       </c>
       <c r="F27">
-        <v>0.0055835</v>
+        <v>0.0064143</v>
       </c>
       <c r="G27">
-        <v>0.00601936</v>
+        <v>0.00695142</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1218,22 +1218,22 @@
         <v>33</v>
       </c>
       <c r="B28">
-        <v>0.006988299999999999</v>
+        <v>0.008450999999999998</v>
       </c>
       <c r="C28">
-        <v>0.0065758</v>
+        <v>0.0077018</v>
       </c>
       <c r="D28">
-        <v>0.004128</v>
+        <v>0.0055859</v>
       </c>
       <c r="E28">
-        <v>0.006358</v>
+        <v>0.0076431</v>
       </c>
       <c r="F28">
-        <v>0.0054782</v>
+        <v>0.0064417</v>
       </c>
       <c r="G28">
-        <v>0.005905659999999999</v>
+        <v>0.0071647</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1241,22 +1241,22 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>0.006968200000000001</v>
+        <v>0.008229999999999999</v>
       </c>
       <c r="C29">
-        <v>0.0059845</v>
+        <v>0.006948900000000001</v>
       </c>
       <c r="D29">
-        <v>0.0045479</v>
+        <v>0.005394100000000001</v>
       </c>
       <c r="E29">
-        <v>0.005843</v>
+        <v>0.006472800000000001</v>
       </c>
       <c r="F29">
-        <v>0.0046185</v>
+        <v>0.0054182</v>
       </c>
       <c r="G29">
-        <v>0.005592420000000001</v>
+        <v>0.0064928</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1264,22 +1264,22 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>0.0300677</v>
+        <v>0.0348928</v>
       </c>
       <c r="C30">
-        <v>0.0173358</v>
+        <v>0.0198398</v>
       </c>
       <c r="D30">
-        <v>0.010331</v>
+        <v>0.0120658</v>
       </c>
       <c r="E30">
-        <v>0.0051314</v>
+        <v>0.006114799999999999</v>
       </c>
       <c r="F30">
-        <v>0.005159200000000001</v>
+        <v>0.0059476</v>
       </c>
       <c r="G30">
-        <v>0.01360502</v>
+        <v>0.01577216</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1287,22 +1287,22 @@
         <v>36</v>
       </c>
       <c r="B31">
-        <v>0.0334449</v>
+        <v>0.03876599999999999</v>
       </c>
       <c r="C31">
-        <v>0.0218867</v>
+        <v>0.0253272</v>
       </c>
       <c r="D31">
-        <v>0.0107913</v>
+        <v>0.0124181</v>
       </c>
       <c r="E31">
-        <v>0.005847199999999999</v>
+        <v>0.0067407</v>
       </c>
       <c r="F31">
-        <v>0.0120979</v>
+        <v>0.0140093</v>
       </c>
       <c r="G31">
-        <v>0.0168136</v>
+        <v>0.01945226</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1310,22 +1310,22 @@
         <v>37</v>
       </c>
       <c r="B32">
-        <v>0.0328473</v>
+        <v>0.0381893</v>
       </c>
       <c r="C32">
-        <v>0.0218362</v>
+        <v>0.0258851</v>
       </c>
       <c r="D32">
-        <v>0.0106905</v>
+        <v>0.0123725</v>
       </c>
       <c r="E32">
-        <v>0.0055382</v>
+        <v>0.006448600000000001</v>
       </c>
       <c r="F32">
-        <v>0.005958199999999999</v>
+        <v>0.007123</v>
       </c>
       <c r="G32">
-        <v>0.01537408</v>
+        <v>0.0180037</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1333,22 +1333,22 @@
         <v>38</v>
       </c>
       <c r="B33">
-        <v>0.0262301</v>
+        <v>0.0301899</v>
       </c>
       <c r="C33">
-        <v>0.0170915</v>
+        <v>0.0195506</v>
       </c>
       <c r="D33">
-        <v>0.013691</v>
+        <v>0.0157564</v>
       </c>
       <c r="E33">
-        <v>0.0183395</v>
+        <v>0.0211243</v>
       </c>
       <c r="F33">
-        <v>0.0204543</v>
+        <v>0.0237573</v>
       </c>
       <c r="G33">
-        <v>0.01916128</v>
+        <v>0.0220757</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1356,22 +1356,22 @@
         <v>39</v>
       </c>
       <c r="B34">
-        <v>0.003945700000000001</v>
+        <v>0.004660699999999999</v>
       </c>
       <c r="C34">
-        <v>0.0034586</v>
+        <v>0.0038658</v>
       </c>
       <c r="D34">
-        <v>0.0023665</v>
+        <v>0.0027164</v>
       </c>
       <c r="E34">
-        <v>0.0033655</v>
+        <v>0.0039857</v>
       </c>
       <c r="F34">
-        <v>0.0064759</v>
+        <v>0.007509399999999999</v>
       </c>
       <c r="G34">
-        <v>0.003922440000000001</v>
+        <v>0.004547600000000001</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1379,22 +1379,22 @@
         <v>40</v>
       </c>
       <c r="B35">
-        <v>0.0028971</v>
+        <v>0.0033268</v>
       </c>
       <c r="C35">
-        <v>0.0030801</v>
+        <v>0.0035534</v>
       </c>
       <c r="D35">
-        <v>0.0027965</v>
+        <v>0.0032308</v>
       </c>
       <c r="E35">
-        <v>0.0029817</v>
+        <v>0.0035506</v>
       </c>
       <c r="F35">
-        <v>0.007276300000000001</v>
+        <v>0.0084502</v>
       </c>
       <c r="G35">
-        <v>0.003806340000000001</v>
+        <v>0.00442236</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1402,22 +1402,22 @@
         <v>41</v>
       </c>
       <c r="B36">
-        <v>0.004717999999999999</v>
+        <v>0.0055517</v>
       </c>
       <c r="C36">
-        <v>0.0031381</v>
+        <v>0.003577</v>
       </c>
       <c r="D36">
-        <v>0.004231</v>
+        <v>0.0048818</v>
       </c>
       <c r="E36">
-        <v>0.0030831</v>
+        <v>0.0038251</v>
       </c>
       <c r="F36">
-        <v>0.006134500000000001</v>
+        <v>0.007148699999999999</v>
       </c>
       <c r="G36">
-        <v>0.00426094</v>
+        <v>0.004996860000000001</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1425,22 +1425,22 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>0.0040164</v>
+        <v>0.0055644</v>
       </c>
       <c r="C37">
-        <v>0.0046449</v>
+        <v>0.0035968</v>
       </c>
       <c r="D37">
-        <v>0.0033271</v>
+        <v>0.0048271</v>
       </c>
       <c r="E37">
-        <v>0.004116399999999999</v>
+        <v>0.0035728</v>
       </c>
       <c r="F37">
-        <v>0.0053754</v>
+        <v>0.0070339</v>
       </c>
       <c r="G37">
-        <v>0.004296039999999999</v>
+        <v>0.004919</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1448,22 +1448,22 @@
         <v>43</v>
       </c>
       <c r="B38">
-        <v>0.004481</v>
+        <v>0.0051029</v>
       </c>
       <c r="C38">
-        <v>0.003381400000000001</v>
+        <v>0.0038632</v>
       </c>
       <c r="D38">
-        <v>0.0020654</v>
+        <v>0.0022884</v>
       </c>
       <c r="E38">
-        <v>0.0025635</v>
+        <v>0.0030507</v>
       </c>
       <c r="F38">
-        <v>0.0037948</v>
+        <v>0.0044633</v>
       </c>
       <c r="G38">
-        <v>0.00325722</v>
+        <v>0.0037537</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1471,22 +1471,22 @@
         <v>44</v>
       </c>
       <c r="B39">
-        <v>0.0037844</v>
+        <v>0.0050469</v>
       </c>
       <c r="C39">
-        <v>0.0032945</v>
+        <v>0.0038247</v>
       </c>
       <c r="D39">
-        <v>0.0020196</v>
+        <v>0.0022725</v>
       </c>
       <c r="E39">
-        <v>0.0024692</v>
+        <v>0.0029388</v>
       </c>
       <c r="F39">
-        <v>0.0037075</v>
+        <v>0.0043435</v>
       </c>
       <c r="G39">
-        <v>0.00305504</v>
+        <v>0.00368528</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1494,22 +1494,22 @@
         <v>45</v>
       </c>
       <c r="B40">
-        <v>0.004443</v>
+        <v>0.005179400000000001</v>
       </c>
       <c r="C40">
-        <v>0.0030184</v>
+        <v>0.0034714</v>
       </c>
       <c r="D40">
-        <v>0.0026348</v>
+        <v>0.0030986</v>
       </c>
       <c r="E40">
-        <v>0.0020174</v>
+        <v>0.0023745</v>
       </c>
       <c r="F40">
-        <v>0.003776</v>
+        <v>0.004379599999999999</v>
       </c>
       <c r="G40">
-        <v>0.003177919999999999</v>
+        <v>0.0037007</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1517,22 +1517,22 @@
         <v>46</v>
       </c>
       <c r="B41">
-        <v>0.006223100000000001</v>
+        <v>0.007234700000000001</v>
       </c>
       <c r="C41">
-        <v>0.0038426</v>
+        <v>0.0044477</v>
       </c>
       <c r="D41">
-        <v>0.004128000000000001</v>
+        <v>0.0047725</v>
       </c>
       <c r="E41">
-        <v>0.0040108</v>
+        <v>0.004706500000000001</v>
       </c>
       <c r="F41">
-        <v>0.006659999999999999</v>
+        <v>0.007750199999999999</v>
       </c>
       <c r="G41">
-        <v>0.0049729</v>
+        <v>0.005782320000000001</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1540,22 +1540,22 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>0.005675599999999999</v>
+        <v>0.007242699999999999</v>
       </c>
       <c r="C42">
-        <v>0.0038327</v>
+        <v>0.004395100000000001</v>
       </c>
       <c r="D42">
-        <v>0.004000200000000001</v>
+        <v>0.004680200000000001</v>
       </c>
       <c r="E42">
-        <v>0.0037012</v>
+        <v>0.0043744</v>
       </c>
       <c r="F42">
-        <v>0.008483200000000002</v>
+        <v>0.007657599999999999</v>
       </c>
       <c r="G42">
-        <v>0.005138580000000001</v>
+        <v>0.00567</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1563,22 +1563,22 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>0.008251400000000001</v>
+        <v>0.0088337</v>
       </c>
       <c r="C43">
-        <v>0.003259500000000001</v>
+        <v>0.0041841</v>
       </c>
       <c r="D43">
-        <v>0.0048312</v>
+        <v>0.005981000000000001</v>
       </c>
       <c r="E43">
-        <v>0.004994699999999999</v>
+        <v>0.0058758</v>
       </c>
       <c r="F43">
-        <v>0.007796200000000001</v>
+        <v>0.0093791</v>
       </c>
       <c r="G43">
-        <v>0.005826599999999999</v>
+        <v>0.006850739999999999</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1586,22 +1586,22 @@
         <v>49</v>
       </c>
       <c r="B44">
-        <v>0.011688</v>
+        <v>0.0136749</v>
       </c>
       <c r="C44">
-        <v>0.009887700000000001</v>
+        <v>0.0115758</v>
       </c>
       <c r="D44">
-        <v>0.0058873</v>
+        <v>0.006827299999999999</v>
       </c>
       <c r="E44">
-        <v>0.0037837</v>
+        <v>0.004426899999999999</v>
       </c>
       <c r="F44">
-        <v>0.0029008</v>
+        <v>0.003349</v>
       </c>
       <c r="G44">
-        <v>0.006829500000000001</v>
+        <v>0.00797078</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1609,22 +1609,22 @@
         <v>50</v>
       </c>
       <c r="B45">
-        <v>0.0117139</v>
+        <v>0.0134884</v>
       </c>
       <c r="C45">
-        <v>0.0145758</v>
+        <v>0.0168217</v>
       </c>
       <c r="D45">
-        <v>0.0070943</v>
+        <v>0.0080626</v>
       </c>
       <c r="E45">
-        <v>0.0042342</v>
+        <v>0.004987800000000001</v>
       </c>
       <c r="F45">
-        <v>0.008473900000000001</v>
+        <v>0.009714199999999999</v>
       </c>
       <c r="G45">
-        <v>0.00921842</v>
+        <v>0.01061494</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1632,22 +1632,22 @@
         <v>51</v>
       </c>
       <c r="B46">
-        <v>0.0109618</v>
+        <v>0.0132261</v>
       </c>
       <c r="C46">
-        <v>0.0149877</v>
+        <v>0.0177573</v>
       </c>
       <c r="D46">
-        <v>0.0067892</v>
+        <v>0.007987600000000001</v>
       </c>
       <c r="E46">
-        <v>0.0041232</v>
+        <v>0.004904899999999999</v>
       </c>
       <c r="F46">
-        <v>0.0035711</v>
+        <v>0.0042278</v>
       </c>
       <c r="G46">
-        <v>0.008086600000000001</v>
+        <v>0.009620739999999999</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1655,22 +1655,22 @@
         <v>52</v>
       </c>
       <c r="B47">
-        <v>0.007335</v>
+        <v>0.008617799999999998</v>
       </c>
       <c r="C47">
-        <v>0.006848299999999999</v>
+        <v>0.008155900000000001</v>
       </c>
       <c r="D47">
-        <v>0.004392699999999999</v>
+        <v>0.0051269</v>
       </c>
       <c r="E47">
-        <v>0.006644600000000001</v>
+        <v>0.007877100000000001</v>
       </c>
       <c r="F47">
-        <v>0.00582</v>
+        <v>0.0068685</v>
       </c>
       <c r="G47">
-        <v>0.006208119999999999</v>
+        <v>0.007329240000000001</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1678,22 +1678,22 @@
         <v>53</v>
       </c>
       <c r="B48">
-        <v>0.0330536</v>
+        <v>0.0384976</v>
       </c>
       <c r="C48">
-        <v>0.0220738</v>
+        <v>0.026071</v>
       </c>
       <c r="D48">
-        <v>0.0113156</v>
+        <v>0.0126335</v>
       </c>
       <c r="E48">
-        <v>0.005725099999999999</v>
+        <v>0.0069665</v>
       </c>
       <c r="F48">
-        <v>0.0063073</v>
+        <v>0.007445199999999999</v>
       </c>
       <c r="G48">
-        <v>0.01569508</v>
+        <v>0.01832276</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1701,22 +1701,22 @@
         <v>54</v>
       </c>
       <c r="B49">
-        <v>0.0040723</v>
+        <v>0.004695799999999999</v>
       </c>
       <c r="C49">
-        <v>0.0034122</v>
+        <v>0.0039474</v>
       </c>
       <c r="D49">
-        <v>0.0024978</v>
+        <v>0.0028094</v>
       </c>
       <c r="E49">
-        <v>0.003502</v>
+        <v>0.0040814</v>
       </c>
       <c r="F49">
-        <v>0.006576900000000001</v>
+        <v>0.0076001</v>
       </c>
       <c r="G49">
-        <v>0.00401224</v>
+        <v>0.004626819999999999</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1724,22 +1724,22 @@
         <v>55</v>
       </c>
       <c r="B50">
-        <v>0.0039064</v>
+        <v>0.004516300000000001</v>
       </c>
       <c r="C50">
-        <v>0.0033126</v>
+        <v>0.003908699999999999</v>
       </c>
       <c r="D50">
-        <v>0.003401</v>
+        <v>0.002792</v>
       </c>
       <c r="E50">
-        <v>0.004187700000000001</v>
+        <v>0.003901599999999999</v>
       </c>
       <c r="F50">
-        <v>0.005499</v>
+        <v>0.0075329</v>
       </c>
       <c r="G50">
-        <v>0.00406134</v>
+        <v>0.004530299999999999</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1747,22 +1747,22 @@
         <v>56</v>
       </c>
       <c r="B51">
-        <v>0.0029469</v>
+        <v>0.0034329</v>
       </c>
       <c r="C51">
-        <v>0.0037448</v>
+        <v>0.0043338</v>
       </c>
       <c r="D51">
-        <v>0.0030594</v>
+        <v>0.003561300000000001</v>
       </c>
       <c r="E51">
-        <v>0.0030911</v>
+        <v>0.003694</v>
       </c>
       <c r="F51">
-        <v>0.0070022</v>
+        <v>0.0080477</v>
       </c>
       <c r="G51">
-        <v>0.003968879999999999</v>
+        <v>0.00461394</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1770,22 +1770,22 @@
         <v>57</v>
       </c>
       <c r="B52">
-        <v>0.0030205</v>
+        <v>0.0034833</v>
       </c>
       <c r="C52">
-        <v>0.0031808</v>
+        <v>0.0036767</v>
       </c>
       <c r="D52">
-        <v>0.002878</v>
+        <v>0.0033354</v>
       </c>
       <c r="E52">
-        <v>0.003085</v>
+        <v>0.0035463</v>
       </c>
       <c r="F52">
-        <v>0.0073606</v>
+        <v>0.0085352</v>
       </c>
       <c r="G52">
-        <v>0.00390498</v>
+        <v>0.00451538</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1793,22 +1793,22 @@
         <v>58</v>
       </c>
       <c r="B53">
-        <v>0.003853</v>
+        <v>0.003385</v>
       </c>
       <c r="C53">
-        <v>0.004409700000000001</v>
+        <v>0.0036119</v>
       </c>
       <c r="D53">
-        <v>0.003489</v>
+        <v>0.0032313</v>
       </c>
       <c r="E53">
-        <v>0.0029235</v>
+        <v>0.0034606</v>
       </c>
       <c r="F53">
-        <v>0.0053676</v>
+        <v>0.008277</v>
       </c>
       <c r="G53">
-        <v>0.00400856</v>
+        <v>0.00439316</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1816,22 +1816,22 @@
         <v>59</v>
       </c>
       <c r="B54">
-        <v>0.0041151</v>
+        <v>0.0055772</v>
       </c>
       <c r="C54">
-        <v>0.0047125</v>
+        <v>0.0036789</v>
       </c>
       <c r="D54">
-        <v>0.0034294</v>
+        <v>0.0049285</v>
       </c>
       <c r="E54">
-        <v>0.0042031</v>
+        <v>0.0036394</v>
       </c>
       <c r="F54">
-        <v>0.005432000000000001</v>
+        <v>0.0070925</v>
       </c>
       <c r="G54">
-        <v>0.004378420000000001</v>
+        <v>0.0049833</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1839,22 +1839,22 @@
         <v>60</v>
       </c>
       <c r="B55">
-        <v>0.0039161</v>
+        <v>0.005191400000000001</v>
       </c>
       <c r="C55">
-        <v>0.0033772</v>
+        <v>0.0038602</v>
       </c>
       <c r="D55">
-        <v>0.0021414</v>
+        <v>0.0023463</v>
       </c>
       <c r="E55">
-        <v>0.0025756</v>
+        <v>0.003022</v>
       </c>
       <c r="F55">
-        <v>0.0038278</v>
+        <v>0.0044007</v>
       </c>
       <c r="G55">
-        <v>0.003167619999999999</v>
+        <v>0.003764120000000001</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1862,22 +1862,22 @@
         <v>61</v>
       </c>
       <c r="B56">
-        <v>0.004534300000000001</v>
+        <v>0.0053915</v>
       </c>
       <c r="C56">
-        <v>0.0030499</v>
+        <v>0.0035837</v>
       </c>
       <c r="D56">
-        <v>0.0027351</v>
+        <v>0.0031481</v>
       </c>
       <c r="E56">
-        <v>0.0021701</v>
+        <v>0.0024519</v>
       </c>
       <c r="F56">
-        <v>0.0038754</v>
+        <v>0.004483200000000001</v>
       </c>
       <c r="G56">
-        <v>0.00327296</v>
+        <v>0.00381168</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1885,22 +1885,22 @@
         <v>62</v>
       </c>
       <c r="B57">
-        <v>0.0044987</v>
+        <v>0.0051659</v>
       </c>
       <c r="C57">
-        <v>0.0030325</v>
+        <v>0.0035263</v>
       </c>
       <c r="D57">
-        <v>0.0027069</v>
+        <v>0.0030647</v>
       </c>
       <c r="E57">
-        <v>0.0019907</v>
+        <v>0.0024029</v>
       </c>
       <c r="F57">
-        <v>0.0038138</v>
+        <v>0.004344099999999999</v>
       </c>
       <c r="G57">
-        <v>0.00320852</v>
+        <v>0.00370078</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1908,22 +1908,22 @@
         <v>63</v>
       </c>
       <c r="B58">
-        <v>0.005797099999999999</v>
+        <v>0.007450299999999998</v>
       </c>
       <c r="C58">
-        <v>0.003862</v>
+        <v>0.0044809</v>
       </c>
       <c r="D58">
-        <v>0.0040983</v>
+        <v>0.004890500000000001</v>
       </c>
       <c r="E58">
-        <v>0.0038092</v>
+        <v>0.0045235</v>
       </c>
       <c r="F58">
-        <v>0.008562900000000002</v>
+        <v>0.007728800000000001</v>
       </c>
       <c r="G58">
-        <v>0.0052259</v>
+        <v>0.0058148</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1931,22 +1931,22 @@
         <v>64</v>
       </c>
       <c r="B59">
-        <v>0.0113934</v>
+        <v>0.0133794</v>
       </c>
       <c r="C59">
-        <v>0.0151418</v>
+        <v>0.0179017</v>
       </c>
       <c r="D59">
-        <v>0.0071785</v>
+        <v>0.008283199999999999</v>
       </c>
       <c r="E59">
-        <v>0.0043406</v>
+        <v>0.0051912</v>
       </c>
       <c r="F59">
-        <v>0.003854899999999999</v>
+        <v>0.0044517</v>
       </c>
       <c r="G59">
-        <v>0.00838184</v>
+        <v>0.00984144</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1954,22 +1954,22 @@
         <v>65</v>
       </c>
       <c r="B60">
-        <v>0.003989499999999999</v>
+        <v>0.0046324</v>
       </c>
       <c r="C60">
-        <v>0.0034596</v>
+        <v>0.003991199999999999</v>
       </c>
       <c r="D60">
-        <v>0.0035047</v>
+        <v>0.0028793</v>
       </c>
       <c r="E60">
-        <v>0.0043237</v>
+        <v>0.0038808</v>
       </c>
       <c r="F60">
-        <v>0.005613599999999999</v>
+        <v>0.0077048</v>
       </c>
       <c r="G60">
-        <v>0.00417822</v>
+        <v>0.0046177</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1977,22 +1977,22 @@
         <v>66</v>
       </c>
       <c r="B61">
-        <v>0.0030456</v>
+        <v>0.0035245</v>
       </c>
       <c r="C61">
-        <v>0.0038207</v>
+        <v>0.004537599999999999</v>
       </c>
       <c r="D61">
-        <v>0.0031707</v>
+        <v>0.0036448</v>
       </c>
       <c r="E61">
-        <v>0.003174300000000001</v>
+        <v>0.0037665</v>
       </c>
       <c r="F61">
-        <v>0.0071022</v>
+        <v>0.008140900000000001</v>
       </c>
       <c r="G61">
-        <v>0.004062700000000001</v>
+        <v>0.00472286</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -2000,22 +2000,22 @@
         <v>67</v>
       </c>
       <c r="B62">
-        <v>0.0034226</v>
+        <v>0.0034772</v>
       </c>
       <c r="C62">
-        <v>0.004093100000000001</v>
+        <v>0.0044184</v>
       </c>
       <c r="D62">
-        <v>0.0037087</v>
+        <v>0.003596</v>
       </c>
       <c r="E62">
-        <v>0.0027353</v>
+        <v>0.0037368</v>
       </c>
       <c r="F62">
-        <v>0.0059132</v>
+        <v>0.008123999999999999</v>
       </c>
       <c r="G62">
-        <v>0.00397458</v>
+        <v>0.00467048</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -2023,22 +2023,22 @@
         <v>68</v>
       </c>
       <c r="B63">
-        <v>0.0039006</v>
+        <v>0.0034502</v>
       </c>
       <c r="C63">
-        <v>0.0044683</v>
+        <v>0.0037038</v>
       </c>
       <c r="D63">
-        <v>0.0036327</v>
+        <v>0.003341</v>
       </c>
       <c r="E63">
-        <v>0.0030463</v>
+        <v>0.0035493</v>
       </c>
       <c r="F63">
-        <v>0.0054604</v>
+        <v>0.008419400000000002</v>
       </c>
       <c r="G63">
-        <v>0.00410166</v>
+        <v>0.00449274</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -2046,22 +2046,22 @@
         <v>69</v>
       </c>
       <c r="B64">
-        <v>0.004568300000000001</v>
+        <v>0.0053302</v>
       </c>
       <c r="C64">
-        <v>0.0030672</v>
+        <v>0.0035866</v>
       </c>
       <c r="D64">
-        <v>0.0027417</v>
+        <v>0.0032395</v>
       </c>
       <c r="E64">
-        <v>0.0021052</v>
+        <v>0.0025207</v>
       </c>
       <c r="F64">
-        <v>0.0038623</v>
+        <v>0.0044793</v>
       </c>
       <c r="G64">
-        <v>0.00326894</v>
+        <v>0.00383126</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -2069,22 +2069,22 @@
         <v>70</v>
       </c>
       <c r="B65">
-        <v>0.0035401</v>
+        <v>0.0035889</v>
       </c>
       <c r="C65">
-        <v>0.0042453</v>
+        <v>0.0044636</v>
       </c>
       <c r="D65">
-        <v>0.0037259</v>
+        <v>0.0036798</v>
       </c>
       <c r="E65">
-        <v>0.0028352</v>
+        <v>0.003812</v>
       </c>
       <c r="F65">
-        <v>0.0060134</v>
+        <v>0.008153499999999999</v>
       </c>
       <c r="G65">
-        <v>0.00407198</v>
+        <v>0.004739559999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2585,7 +2585,7 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C22">
         <v>19</v>
@@ -2600,7 +2600,7 @@
         <v>12</v>
       </c>
       <c r="G22">
-        <v>19.2</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2755,13 +2755,13 @@
         <v>15</v>
       </c>
       <c r="E29">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F29">
         <v>4</v>
       </c>
       <c r="G29">
-        <v>9</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2930,22 +2930,22 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C37">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D37">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E37">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F37">
         <v>16</v>
       </c>
       <c r="G37">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -3045,7 +3045,7 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C42">
         <v>19</v>
@@ -3057,10 +3057,10 @@
         <v>24</v>
       </c>
       <c r="F42">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G42">
-        <v>20</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3068,7 +3068,7 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C43">
         <v>11</v>
@@ -3083,7 +3083,7 @@
         <v>4</v>
       </c>
       <c r="G43">
-        <v>10.2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3229,22 +3229,22 @@
         <v>55</v>
       </c>
       <c r="B50">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C50">
         <v>20</v>
       </c>
       <c r="D50">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E50">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F50">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G50">
-        <v>19</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -3301,19 +3301,19 @@
         <v>18</v>
       </c>
       <c r="C53">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D53">
         <v>24</v>
       </c>
       <c r="E53">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F53">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G53">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3321,22 +3321,22 @@
         <v>59</v>
       </c>
       <c r="B54">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C54">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D54">
+        <v>15</v>
+      </c>
+      <c r="E54">
         <v>9</v>
-      </c>
-      <c r="E54">
-        <v>11</v>
       </c>
       <c r="F54">
         <v>4</v>
       </c>
       <c r="G54">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -3413,7 +3413,7 @@
         <v>63</v>
       </c>
       <c r="B58">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C58">
         <v>11</v>
@@ -3425,10 +3425,10 @@
         <v>11</v>
       </c>
       <c r="F58">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G58">
-        <v>11</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3459,22 +3459,22 @@
         <v>65</v>
       </c>
       <c r="B60">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C60">
         <v>12</v>
       </c>
       <c r="D60">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E60">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F60">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G60">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3508,19 +3508,19 @@
         <v>18</v>
       </c>
       <c r="C62">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D62">
         <v>24</v>
       </c>
       <c r="E62">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F62">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G62">
-        <v>19.8</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3531,19 +3531,19 @@
         <v>12</v>
       </c>
       <c r="C63">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D63">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E63">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F63">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G63">
-        <v>10.8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3577,19 +3577,19 @@
         <v>12</v>
       </c>
       <c r="C65">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D65">
         <v>16</v>
       </c>
       <c r="E65">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F65">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G65">
-        <v>11.8</v>
+        <v>11.2</v>
       </c>
     </row>
   </sheetData>
@@ -4090,7 +4090,7 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>111.9827560572969</v>
+        <v>105.4974746830583</v>
       </c>
       <c r="C22">
         <v>103.9827560572969</v>
@@ -4105,7 +4105,7 @@
         <v>96.12489168102785</v>
       </c>
       <c r="G22">
-        <v>103.2111831820431</v>
+        <v>101.9141269071954</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -4260,13 +4260,13 @@
         <v>102.0661260637976</v>
       </c>
       <c r="E29">
-        <v>95.10870539248485</v>
+        <v>95.99372086918898</v>
       </c>
       <c r="F29">
         <v>93.1180579165468</v>
       </c>
       <c r="G29">
-        <v>98.45886634529195</v>
+        <v>98.63586944063277</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -4435,22 +4435,22 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>111.9827560572969</v>
+        <v>105.4974746830583</v>
       </c>
       <c r="C37">
-        <v>107.1543289325507</v>
+        <v>103.9827560572969</v>
       </c>
       <c r="D37">
-        <v>110.1837661840736</v>
+        <v>105.4974746830583</v>
       </c>
       <c r="E37">
-        <v>101.6396103067893</v>
+        <v>98.46803743153546</v>
       </c>
       <c r="F37">
         <v>96.12489168102785</v>
       </c>
       <c r="G37">
-        <v>105.4170706323477</v>
+        <v>101.9141269071954</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -4550,7 +4550,7 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>111.9827560572969</v>
+        <v>107.8406204335659</v>
       </c>
       <c r="C42">
         <v>103.9827560572969</v>
@@ -4562,10 +4562,10 @@
         <v>98.46803743153546</v>
       </c>
       <c r="F42">
-        <v>98.46803743153546</v>
+        <v>96.12489168102785</v>
       </c>
       <c r="G42">
-        <v>103.6798123321446</v>
+        <v>102.3827560572969</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -4573,7 +4573,7 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>110.5575913783105</v>
+        <v>104.0723100040719</v>
       </c>
       <c r="C43">
         <v>102.4457053266944</v>
@@ -4588,7 +4588,7 @@
         <v>95.17930953468691</v>
       </c>
       <c r="G43">
-        <v>101.4818639482212</v>
+        <v>100.1848076733735</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -4671,7 +4671,7 @@
         <v>103.3271534819307</v>
       </c>
       <c r="D47">
-        <v>104.3277853366118</v>
+        <v>104.5993450099368</v>
       </c>
       <c r="E47">
         <v>95.17284061197759</v>
@@ -4680,7 +4680,7 @@
         <v>94.58282965890581</v>
       </c>
       <c r="G47">
-        <v>101.3743625512961</v>
+        <v>101.4286744859611</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -4734,22 +4734,22 @@
         <v>55</v>
       </c>
       <c r="B50">
-        <v>111.9827560572969</v>
+        <v>132.2253967444162</v>
       </c>
       <c r="C50">
-        <v>107.1543289325507</v>
+        <v>108.6690475583121</v>
       </c>
       <c r="D50">
-        <v>110.1837661840736</v>
+        <v>105.4974746830583</v>
       </c>
       <c r="E50">
         <v>98.46803743153546</v>
       </c>
       <c r="F50">
-        <v>96.12489168102785</v>
+        <v>100.8111831820431</v>
       </c>
       <c r="G50">
-        <v>104.7827560572969</v>
+        <v>109.134227919873</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -4806,19 +4806,19 @@
         <v>111.9827560572969</v>
       </c>
       <c r="C53">
-        <v>119.39696961967</v>
+        <v>108.6690475583121</v>
       </c>
       <c r="D53">
-        <v>105.4974746830583</v>
+        <v>108.6690475583121</v>
       </c>
       <c r="E53">
-        <v>101.6396103067893</v>
+        <v>98.46803743153546</v>
       </c>
       <c r="F53">
-        <v>96.12489168102785</v>
+        <v>100.8111831820431</v>
       </c>
       <c r="G53">
-        <v>106.9283404695685</v>
+        <v>105.7200143574999</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -4826,22 +4826,22 @@
         <v>59</v>
       </c>
       <c r="B54">
-        <v>110.934942379664</v>
+        <v>102.3440997142822</v>
       </c>
       <c r="C54">
-        <v>105.2369118846929</v>
+        <v>100.9779513093111</v>
       </c>
       <c r="D54">
-        <v>107.3529870742077</v>
+        <v>102.6712897929513</v>
       </c>
       <c r="E54">
-        <v>98.46403379269465</v>
+        <v>95.64392974814447</v>
       </c>
       <c r="F54">
         <v>93.1180579165468</v>
       </c>
       <c r="G54">
-        <v>103.0213866095612</v>
+        <v>98.95106569624718</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -4918,7 +4918,7 @@
         <v>63</v>
       </c>
       <c r="B58">
-        <v>110.5575913783105</v>
+        <v>106.4154557545795</v>
       </c>
       <c r="C58">
         <v>102.4457053266944</v>
@@ -4930,10 +4930,10 @@
         <v>94.35610639961114</v>
       </c>
       <c r="F58">
-        <v>95.6963231731842</v>
+        <v>95.17930953468691</v>
       </c>
       <c r="G58">
-        <v>101.5852666759206</v>
+        <v>100.653436823475</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -4964,22 +4964,22 @@
         <v>65</v>
       </c>
       <c r="B60">
-        <v>110.934942379664</v>
+        <v>114.2596075487725</v>
       </c>
       <c r="C60">
-        <v>105.2369118846929</v>
+        <v>105.108348609036</v>
       </c>
       <c r="D60">
-        <v>107.3529870742077</v>
+        <v>103.6168719392922</v>
       </c>
       <c r="E60">
-        <v>96.7154439082003</v>
+        <v>94.40672336061202</v>
       </c>
       <c r="F60">
-        <v>93.1180579165468</v>
+        <v>96.35556830690527</v>
       </c>
       <c r="G60">
-        <v>102.6716686326623</v>
+        <v>102.7494239529236</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -5013,19 +5013,19 @@
         <v>111.9827560572969</v>
       </c>
       <c r="C62">
-        <v>103.9827560572969</v>
+        <v>108.6690475583121</v>
       </c>
       <c r="D62">
         <v>108.6690475583121</v>
       </c>
       <c r="E62">
-        <v>101.6396103067893</v>
+        <v>98.46803743153546</v>
       </c>
       <c r="F62">
-        <v>113.3553390593274</v>
+        <v>100.8111831820431</v>
       </c>
       <c r="G62">
-        <v>107.9259018078045</v>
+        <v>105.7200143574999</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -5036,19 +5036,19 @@
         <v>110.934942379664</v>
       </c>
       <c r="C63">
-        <v>103.3028666066464</v>
+        <v>105.108348609036</v>
       </c>
       <c r="D63">
-        <v>103.6168719392922</v>
+        <v>106.8493377268543</v>
       </c>
       <c r="E63">
-        <v>98.44713706158336</v>
+        <v>95.64392974814447</v>
       </c>
       <c r="F63">
-        <v>93.1180579165468</v>
+        <v>96.35556830690527</v>
       </c>
       <c r="G63">
-        <v>101.8839751807465</v>
+        <v>102.9784253541208</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -5082,19 +5082,19 @@
         <v>110.934942379664</v>
       </c>
       <c r="C65">
-        <v>100.9779513093111</v>
+        <v>105.108348609036</v>
       </c>
       <c r="D65">
-        <v>107.6902241629822</v>
+        <v>106.8493377268543</v>
       </c>
       <c r="E65">
-        <v>98.44713706158336</v>
+        <v>95.64392974814447</v>
       </c>
       <c r="F65">
-        <v>110.3485052948463</v>
+        <v>95.52841180524675</v>
       </c>
       <c r="G65">
-        <v>105.6797520416774</v>
+        <v>102.8129940537891</v>
       </c>
     </row>
   </sheetData>
@@ -5273,22 +5273,22 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C8">
         <v>138</v>
       </c>
       <c r="D8">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E8">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="F8">
-        <v>526</v>
+        <v>503</v>
       </c>
       <c r="G8">
-        <v>249.4</v>
+        <v>240.6</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -5365,22 +5365,22 @@
         <v>17</v>
       </c>
       <c r="B12">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C12">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D12">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E12">
-        <v>314</v>
+        <v>275</v>
       </c>
       <c r="F12">
-        <v>406</v>
+        <v>375</v>
       </c>
       <c r="G12">
-        <v>270.4</v>
+        <v>255.4</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -5411,22 +5411,22 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C14">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="D14">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E14">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F14">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G14">
-        <v>237.4</v>
+        <v>233.6</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -5480,22 +5480,22 @@
         <v>22</v>
       </c>
       <c r="B17">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C17">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="D17">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E17">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="F17">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="G17">
-        <v>269</v>
+        <v>264</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -5595,22 +5595,22 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C22">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D22">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E22">
         <v>25</v>
       </c>
       <c r="F22">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G22">
-        <v>14.6</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -5618,22 +5618,22 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C23">
         <v>138</v>
       </c>
       <c r="D23">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E23">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="F23">
-        <v>526</v>
+        <v>503</v>
       </c>
       <c r="G23">
-        <v>249.4</v>
+        <v>240.6</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -5664,22 +5664,22 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="C25">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="D25">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E25">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F25">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G25">
-        <v>232.6</v>
+        <v>227.4</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -5733,22 +5733,22 @@
         <v>33</v>
       </c>
       <c r="B28">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C28">
         <v>174</v>
       </c>
       <c r="D28">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E28">
         <v>244</v>
       </c>
       <c r="F28">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G28">
-        <v>219</v>
+        <v>217.2</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -5756,22 +5756,22 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C29">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D29">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E29">
-        <v>314</v>
+        <v>275</v>
       </c>
       <c r="F29">
-        <v>406</v>
+        <v>375</v>
       </c>
       <c r="G29">
-        <v>270.4</v>
+        <v>255.4</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -5779,22 +5779,22 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C30">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="D30">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E30">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F30">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G30">
-        <v>237.4</v>
+        <v>233.6</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -5825,22 +5825,22 @@
         <v>37</v>
       </c>
       <c r="B32">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C32">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D32">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E32">
         <v>226</v>
       </c>
       <c r="F32">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="G32">
-        <v>229.4</v>
+        <v>228.6</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -5848,22 +5848,22 @@
         <v>38</v>
       </c>
       <c r="B33">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C33">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="D33">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E33">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="F33">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="G33">
-        <v>269</v>
+        <v>264</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -5940,22 +5940,22 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C37">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D37">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E37">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F37">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G37">
-        <v>17.2</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -5986,7 +5986,7 @@
         <v>44</v>
       </c>
       <c r="B39">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C39">
         <v>15</v>
@@ -6001,7 +6001,7 @@
         <v>7</v>
       </c>
       <c r="G39">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -6055,7 +6055,7 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C42">
         <v>16</v>
@@ -6067,10 +6067,10 @@
         <v>24</v>
       </c>
       <c r="F42">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G42">
-        <v>15.6</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -6078,22 +6078,22 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C43">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D43">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E43">
         <v>25</v>
       </c>
       <c r="F43">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G43">
-        <v>14.6</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -6101,22 +6101,22 @@
         <v>49</v>
       </c>
       <c r="B44">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="C44">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="D44">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E44">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F44">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G44">
-        <v>232.6</v>
+        <v>227.4</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -6147,22 +6147,22 @@
         <v>51</v>
       </c>
       <c r="B46">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C46">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D46">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E46">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F46">
         <v>266</v>
       </c>
       <c r="G46">
-        <v>243.6</v>
+        <v>242.6</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -6170,22 +6170,22 @@
         <v>52</v>
       </c>
       <c r="B47">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C47">
         <v>174</v>
       </c>
       <c r="D47">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E47">
         <v>244</v>
       </c>
       <c r="F47">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G47">
-        <v>219</v>
+        <v>217.2</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -6193,22 +6193,22 @@
         <v>53</v>
       </c>
       <c r="B48">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C48">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D48">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E48">
         <v>226</v>
       </c>
       <c r="F48">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="G48">
-        <v>229.4</v>
+        <v>228.6</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -6239,22 +6239,22 @@
         <v>55</v>
       </c>
       <c r="B50">
+        <v>18</v>
+      </c>
+      <c r="C50">
+        <v>17</v>
+      </c>
+      <c r="D50">
         <v>13</v>
       </c>
-      <c r="C50">
-        <v>15</v>
-      </c>
-      <c r="D50">
-        <v>16</v>
-      </c>
       <c r="E50">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F50">
         <v>15</v>
       </c>
       <c r="G50">
-        <v>17.8</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -6308,22 +6308,22 @@
         <v>58</v>
       </c>
       <c r="B53">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C53">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D53">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E53">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F53">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G53">
-        <v>19.2</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -6331,22 +6331,22 @@
         <v>59</v>
       </c>
       <c r="B54">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C54">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D54">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E54">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F54">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G54">
-        <v>17.2</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -6354,7 +6354,7 @@
         <v>60</v>
       </c>
       <c r="B55">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C55">
         <v>15</v>
@@ -6369,7 +6369,7 @@
         <v>7</v>
       </c>
       <c r="G55">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -6423,7 +6423,7 @@
         <v>63</v>
       </c>
       <c r="B58">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C58">
         <v>16</v>
@@ -6435,10 +6435,10 @@
         <v>24</v>
       </c>
       <c r="F58">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G58">
-        <v>15.6</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -6446,22 +6446,22 @@
         <v>64</v>
       </c>
       <c r="B59">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C59">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D59">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E59">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F59">
         <v>266</v>
       </c>
       <c r="G59">
-        <v>243.6</v>
+        <v>242.6</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -6469,22 +6469,22 @@
         <v>65</v>
       </c>
       <c r="B60">
+        <v>18</v>
+      </c>
+      <c r="C60">
+        <v>17</v>
+      </c>
+      <c r="D60">
         <v>13</v>
       </c>
-      <c r="C60">
-        <v>15</v>
-      </c>
-      <c r="D60">
-        <v>16</v>
-      </c>
       <c r="E60">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F60">
         <v>15</v>
       </c>
       <c r="G60">
-        <v>17.8</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -6515,19 +6515,19 @@
         <v>67</v>
       </c>
       <c r="B62">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C62">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D62">
         <v>20</v>
       </c>
       <c r="E62">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F62">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G62">
         <v>18.2</v>
@@ -6538,22 +6538,22 @@
         <v>68</v>
       </c>
       <c r="B63">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C63">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D63">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E63">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F63">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G63">
-        <v>19.2</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -6584,19 +6584,19 @@
         <v>70</v>
       </c>
       <c r="B65">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C65">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D65">
         <v>20</v>
       </c>
       <c r="E65">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F65">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G65">
         <v>18.2</v>
@@ -6870,22 +6870,22 @@
         <v>17</v>
       </c>
       <c r="B12">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="C12">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D12">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E12">
-        <v>797</v>
+        <v>814</v>
       </c>
       <c r="F12">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="G12">
-        <v>806.2</v>
+        <v>808.2</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -6919,7 +6919,7 @@
         <v>738</v>
       </c>
       <c r="C14">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D14">
         <v>320</v>
@@ -6931,7 +6931,7 @@
         <v>124</v>
       </c>
       <c r="G14">
-        <v>344.2</v>
+        <v>344.4</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -7100,10 +7100,10 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C22">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D22">
         <v>60</v>
@@ -7115,7 +7115,7 @@
         <v>28</v>
       </c>
       <c r="G22">
-        <v>50</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -7172,19 +7172,19 @@
         <v>682</v>
       </c>
       <c r="C25">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="D25">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E25">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F25">
         <v>119</v>
       </c>
       <c r="G25">
-        <v>368.6</v>
+        <v>369.6</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -7238,7 +7238,7 @@
         <v>33</v>
       </c>
       <c r="B28">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C28">
         <v>789</v>
@@ -7250,10 +7250,10 @@
         <v>743</v>
       </c>
       <c r="F28">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="G28">
-        <v>694</v>
+        <v>693.4</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -7261,22 +7261,22 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="C29">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D29">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E29">
-        <v>797</v>
+        <v>814</v>
       </c>
       <c r="F29">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="G29">
-        <v>806.2</v>
+        <v>808.2</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -7287,7 +7287,7 @@
         <v>738</v>
       </c>
       <c r="C30">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D30">
         <v>320</v>
@@ -7299,7 +7299,7 @@
         <v>124</v>
       </c>
       <c r="G30">
-        <v>344.2</v>
+        <v>344.4</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -7330,22 +7330,22 @@
         <v>37</v>
       </c>
       <c r="B32">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C32">
         <v>529</v>
       </c>
       <c r="D32">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E32">
         <v>134</v>
       </c>
       <c r="F32">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G32">
-        <v>371.2</v>
+        <v>371.6</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -7445,22 +7445,22 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C37">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="D37">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E37">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F37">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G37">
-        <v>40.8</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -7491,7 +7491,7 @@
         <v>44</v>
       </c>
       <c r="B39">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C39">
         <v>40</v>
@@ -7506,7 +7506,7 @@
         <v>17</v>
       </c>
       <c r="G39">
-        <v>29.8</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -7560,22 +7560,22 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C42">
         <v>44</v>
       </c>
       <c r="D42">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E42">
         <v>48</v>
       </c>
       <c r="F42">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G42">
-        <v>46</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -7583,10 +7583,10 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C43">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D43">
         <v>60</v>
@@ -7598,7 +7598,7 @@
         <v>28</v>
       </c>
       <c r="G43">
-        <v>50</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -7609,19 +7609,19 @@
         <v>682</v>
       </c>
       <c r="C44">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="D44">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E44">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F44">
         <v>119</v>
       </c>
       <c r="G44">
-        <v>368.6</v>
+        <v>369.6</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -7652,22 +7652,22 @@
         <v>51</v>
       </c>
       <c r="B46">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="C46">
         <v>697</v>
       </c>
       <c r="D46">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E46">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F46">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G46">
-        <v>395.2</v>
+        <v>396</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -7675,7 +7675,7 @@
         <v>52</v>
       </c>
       <c r="B47">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C47">
         <v>789</v>
@@ -7687,10 +7687,10 @@
         <v>743</v>
       </c>
       <c r="F47">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="G47">
-        <v>694</v>
+        <v>693.4</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -7698,22 +7698,22 @@
         <v>53</v>
       </c>
       <c r="B48">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C48">
         <v>529</v>
       </c>
       <c r="D48">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E48">
         <v>134</v>
       </c>
       <c r="F48">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G48">
-        <v>371.2</v>
+        <v>371.6</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -7744,22 +7744,22 @@
         <v>55</v>
       </c>
       <c r="B50">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C50">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D50">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="E50">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="F50">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G50">
-        <v>35.6</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -7813,22 +7813,22 @@
         <v>58</v>
       </c>
       <c r="B53">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C53">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="D53">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E53">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F53">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G53">
-        <v>35</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -7836,22 +7836,22 @@
         <v>59</v>
       </c>
       <c r="B54">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C54">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="D54">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E54">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F54">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G54">
-        <v>40.8</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -7859,7 +7859,7 @@
         <v>60</v>
       </c>
       <c r="B55">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C55">
         <v>40</v>
@@ -7874,7 +7874,7 @@
         <v>17</v>
       </c>
       <c r="G55">
-        <v>29.8</v>
+        <v>31</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -7928,22 +7928,22 @@
         <v>63</v>
       </c>
       <c r="B58">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C58">
         <v>44</v>
       </c>
       <c r="D58">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E58">
         <v>48</v>
       </c>
       <c r="F58">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G58">
-        <v>46</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -7951,22 +7951,22 @@
         <v>64</v>
       </c>
       <c r="B59">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="C59">
         <v>697</v>
       </c>
       <c r="D59">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E59">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F59">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G59">
-        <v>395.2</v>
+        <v>396</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -7974,22 +7974,22 @@
         <v>65</v>
       </c>
       <c r="B60">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C60">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D60">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="E60">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="F60">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G60">
-        <v>35.6</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -8020,22 +8020,22 @@
         <v>67</v>
       </c>
       <c r="B62">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C62">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D62">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E62">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F62">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G62">
-        <v>32.2</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -8043,22 +8043,22 @@
         <v>68</v>
       </c>
       <c r="B63">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C63">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="D63">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E63">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F63">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G63">
-        <v>35</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -8089,22 +8089,22 @@
         <v>70</v>
       </c>
       <c r="B65">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C65">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D65">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E65">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F65">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G65">
-        <v>32.2</v>
+        <v>31.4</v>
       </c>
     </row>
   </sheetData>
@@ -8378,7 +8378,7 @@
         <v>8</v>
       </c>
       <c r="C12">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D12">
         <v>18</v>
@@ -8390,7 +8390,7 @@
         <v>6</v>
       </c>
       <c r="G12">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -8605,7 +8605,7 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C22">
         <v>11</v>
@@ -8620,7 +8620,7 @@
         <v>3</v>
       </c>
       <c r="G22">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -8677,7 +8677,7 @@
         <v>14</v>
       </c>
       <c r="C25">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D25">
         <v>18</v>
@@ -8689,7 +8689,7 @@
         <v>8</v>
       </c>
       <c r="G25">
-        <v>13.2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -8775,13 +8775,13 @@
         <v>13</v>
       </c>
       <c r="E29">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F29">
         <v>2</v>
       </c>
       <c r="G29">
-        <v>7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -8950,22 +8950,22 @@
         <v>42</v>
       </c>
       <c r="B37">
+        <v>6</v>
+      </c>
+      <c r="C37">
+        <v>12</v>
+      </c>
+      <c r="D37">
+        <v>14</v>
+      </c>
+      <c r="E37">
         <v>10</v>
-      </c>
-      <c r="C37">
-        <v>14</v>
-      </c>
-      <c r="D37">
-        <v>8</v>
-      </c>
-      <c r="E37">
-        <v>12</v>
       </c>
       <c r="F37">
         <v>4</v>
       </c>
       <c r="G37">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -9065,7 +9065,7 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C42">
         <v>11</v>
@@ -9077,10 +9077,10 @@
         <v>13</v>
       </c>
       <c r="F42">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G42">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -9088,7 +9088,7 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C43">
         <v>9</v>
@@ -9103,7 +9103,7 @@
         <v>2</v>
       </c>
       <c r="G43">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -9249,22 +9249,22 @@
         <v>55</v>
       </c>
       <c r="B50">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C50">
         <v>14</v>
       </c>
       <c r="D50">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E50">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F50">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G50">
-        <v>9</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -9321,19 +9321,19 @@
         <v>10</v>
       </c>
       <c r="C53">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D53">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E53">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F53">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G53">
-        <v>11</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -9341,22 +9341,22 @@
         <v>59</v>
       </c>
       <c r="B54">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C54">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D54">
+        <v>13</v>
+      </c>
+      <c r="E54">
         <v>7</v>
-      </c>
-      <c r="E54">
-        <v>9</v>
       </c>
       <c r="F54">
         <v>2</v>
       </c>
       <c r="G54">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -9433,7 +9433,7 @@
         <v>63</v>
       </c>
       <c r="B58">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C58">
         <v>9</v>
@@ -9445,10 +9445,10 @@
         <v>9</v>
       </c>
       <c r="F58">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G58">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -9479,22 +9479,22 @@
         <v>65</v>
       </c>
       <c r="B60">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C60">
         <v>10</v>
       </c>
       <c r="D60">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E60">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F60">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G60">
-        <v>7.2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -9528,19 +9528,19 @@
         <v>10</v>
       </c>
       <c r="C62">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D62">
         <v>16</v>
       </c>
       <c r="E62">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F62">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G62">
-        <v>12</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -9551,19 +9551,19 @@
         <v>10</v>
       </c>
       <c r="C63">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D63">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E63">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G63">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -9597,19 +9597,19 @@
         <v>10</v>
       </c>
       <c r="C65">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D65">
         <v>14</v>
       </c>
       <c r="E65">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F65">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G65">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
   </sheetData>
